--- a/data/05_modelado/results/results_boosting.xlsx
+++ b/data/05_modelado/results/results_boosting.xlsx
@@ -542,63 +542,63 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7861853076417151</v>
+        <v>0.8317326001672022</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004214369557038035</v>
+        <v>0.003983930847886074</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9318107808306586</v>
+        <v>0.9537035966611166</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003240052843877967</v>
+        <v>0.001773359836655011</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8485475672104397</v>
+        <v>0.874027598124419</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7326457993894749</v>
+        <v>0.7935408590485407</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8834770285932281</v>
+        <v>0.9060825902190193</v>
       </c>
       <c r="K2" t="n">
-        <v>8.340999999999999</v>
+        <v>16.899</v>
       </c>
       <c r="L2" t="n">
-        <v>5.01</v>
+        <v>6.65</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7645</v>
+        <v>0.8336</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9242</v>
+        <v>0.9573</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8354</v>
+        <v>0.8692</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7046</v>
+        <v>0.8007</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.873</v>
+        <v>0.9065</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6784</v>
+        <v>0.7687</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3026</v>
+        <v>0.2325</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -607,52 +607,52 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7865254210379804</v>
+        <v>0.8259156953118418</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00404726089486917</v>
+        <v>0.00358620689183591</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9314043328872905</v>
+        <v>0.9530835320729514</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003268597955859321</v>
+        <v>0.002143235763700093</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8490216740390399</v>
+        <v>0.7935193910772284</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7329001713314985</v>
+        <v>0.8611740690867409</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8836629160213443</v>
+        <v>0.8938130869670085</v>
       </c>
       <c r="K3" t="n">
-        <v>14.638</v>
+        <v>10.126</v>
       </c>
       <c r="L3" t="n">
-        <v>5.01</v>
+        <v>6.65</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7815</v>
+        <v>0.8298</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9263</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8456</v>
+        <v>0.7882</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7265</v>
+        <v>0.876</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8812</v>
+        <v>0.8949</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7006</v>
+        <v>0.754</v>
       </c>
       <c r="S3" t="n">
-        <v>0.299</v>
+        <v>0.2549</v>
       </c>
     </row>
     <row r="4">
@@ -663,7 +663,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>smote</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -672,52 +672,52 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7870025454862608</v>
+        <v>0.8303908161318067</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005539922661320788</v>
+        <v>0.004960968429522507</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9311910835773167</v>
+        <v>0.952742401153302</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003317252667101671</v>
+        <v>0.001911927986702732</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7545675339196789</v>
+        <v>0.8538239701866471</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8226533198809969</v>
+        <v>0.808414387968506</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8697947062478273</v>
+        <v>0.9034056232726609</v>
       </c>
       <c r="K4" t="n">
-        <v>9.345000000000001</v>
+        <v>8.996</v>
       </c>
       <c r="L4" t="n">
-        <v>5.01</v>
+        <v>6.65</v>
       </c>
       <c r="M4" t="n">
-        <v>0.77</v>
+        <v>0.829</v>
       </c>
       <c r="N4" t="n">
-        <v>0.923</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7289</v>
+        <v>0.844</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8144</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.9016999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6671</v>
+        <v>0.76</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3356</v>
+        <v>0.2365</v>
       </c>
     </row>
     <row r="5">
@@ -728,7 +728,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -737,63 +737,63 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7855424675554907</v>
+        <v>0.8275310690545604</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002488758031695132</v>
+        <v>0.005032620104307153</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9308911136203069</v>
+        <v>0.9521450064881061</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002936380163272879</v>
+        <v>0.001421577006580887</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7465867680398576</v>
+        <v>0.8694951037985138</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8290104374082657</v>
+        <v>0.7896000730238919</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8676382683311322</v>
+        <v>0.9037402095855354</v>
       </c>
       <c r="K5" t="n">
-        <v>14.293</v>
+        <v>25.148</v>
       </c>
       <c r="L5" t="n">
-        <v>5.01</v>
+        <v>6.65</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7725</v>
+        <v>0.8334</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9261</v>
+        <v>0.9564</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7282</v>
+        <v>0.8641</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8226</v>
+        <v>0.8048</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8583</v>
+        <v>0.9059</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6701</v>
+        <v>0.7679</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3337</v>
+        <v>0.2357</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>smote</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -802,52 +802,52 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7912076238273901</v>
+        <v>0.8243113937095341</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004430685515000163</v>
+        <v>0.00332940937553879</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9301020627141068</v>
+        <v>0.9519103293169776</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003615020362795819</v>
+        <v>0.001557221927747491</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8233056141907756</v>
+        <v>0.7834979572897383</v>
       </c>
       <c r="I6" t="n">
-        <v>0.761759391122912</v>
+        <v>0.8696920960522669</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8823987612572921</v>
+        <v>0.8915822788746819</v>
       </c>
       <c r="K6" t="n">
-        <v>10.57</v>
+        <v>16.487</v>
       </c>
       <c r="L6" t="n">
-        <v>5.01</v>
+        <v>6.65</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7691</v>
+        <v>0.8244</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9222</v>
+        <v>0.9567</v>
       </c>
       <c r="O6" t="n">
-        <v>0.762</v>
+        <v>0.7766</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7763</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8636</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6723</v>
+        <v>0.7454</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3156</v>
+        <v>0.2621</v>
       </c>
     </row>
     <row r="7">
@@ -867,52 +867,52 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7855041140985022</v>
+        <v>0.8271588510229348</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002663098842694002</v>
+        <v>0.00510875703307486</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9295569988554219</v>
+        <v>0.9511099837908592</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003125262472040333</v>
+        <v>0.001457607870015335</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8201749687954146</v>
+        <v>0.8482930033478343</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7538773344017654</v>
+        <v>0.8072708047410601</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8795730885150913</v>
+        <v>0.9013234725985884</v>
       </c>
       <c r="K7" t="n">
-        <v>19.323</v>
+        <v>19.148</v>
       </c>
       <c r="L7" t="n">
-        <v>5.01</v>
+        <v>6.65</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7788</v>
+        <v>0.8279</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9242</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7798</v>
+        <v>0.8418</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7778</v>
+        <v>0.8144</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8708</v>
+        <v>0.901</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6876</v>
+        <v>0.7584</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3116</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="8">
@@ -923,7 +923,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,52 +932,52 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7811163067495628</v>
+        <v>0.8223499537643276</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006795949429838209</v>
+        <v>0.00331651332297705</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9291247191504812</v>
+        <v>0.9496473590790206</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003320779901018898</v>
+        <v>0.001591566008043649</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8527291742676015</v>
+        <v>0.7822586669537891</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7209492944389559</v>
+        <v>0.8668948124764227</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8818781562057042</v>
+        <v>0.8904668851951449</v>
       </c>
       <c r="K8" t="n">
-        <v>21.669</v>
+        <v>34.533</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7766</v>
+        <v>0.8188</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9255</v>
+        <v>0.953</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.7702</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7219</v>
+        <v>0.8739</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8784999999999999</v>
+        <v>0.8868</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6938</v>
+        <v>0.737</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2979</v>
+        <v>0.2746</v>
       </c>
     </row>
     <row r="9">
@@ -988,7 +988,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -997,52 +997,52 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7847601758073608</v>
+        <v>0.8218303735581662</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006420774015971335</v>
+        <v>0.005615591251413946</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9286477102997148</v>
+        <v>0.9495410566153544</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003302395485081426</v>
+        <v>0.001841139854607562</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7438051311286004</v>
+        <v>0.8744512182239209</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8306625221838344</v>
+        <v>0.7753606564395522</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8667830216779974</v>
+        <v>0.9016952267215682</v>
       </c>
       <c r="K9" t="n">
-        <v>21.118</v>
+        <v>27.511</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>6.63</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.8274</v>
       </c>
       <c r="N9" t="n">
-        <v>0.923</v>
+        <v>0.9536</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7429</v>
+        <v>0.8691</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8094</v>
+        <v>0.7895</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8623</v>
+        <v>0.9036</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6758</v>
+        <v>0.7608</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3261</v>
+        <v>0.2425</v>
       </c>
     </row>
     <row r="10">
@@ -1062,52 +1062,52 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7857817865369323</v>
+        <v>0.8234345236250021</v>
       </c>
       <c r="E10" t="n">
-        <v>0.006122454155172192</v>
+        <v>0.004391626251727939</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9277165208629947</v>
+        <v>0.9492213590114341</v>
       </c>
       <c r="G10" t="n">
-        <v>0.004115470851487426</v>
+        <v>0.001707534404035993</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8165921484640132</v>
+        <v>0.8459320523351781</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7574357143376436</v>
+        <v>0.8023123693910341</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8792383156029471</v>
+        <v>0.8993900899201147</v>
       </c>
       <c r="K10" t="n">
-        <v>18.515</v>
+        <v>47.524</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7742</v>
+        <v>0.8244</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9233</v>
+        <v>0.9519</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7788</v>
+        <v>0.8389</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.8104</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8687</v>
+        <v>0.899</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6817</v>
+        <v>0.7536</v>
       </c>
       <c r="S10" t="n">
-        <v>0.308</v>
+        <v>0.2501</v>
       </c>
     </row>
     <row r="11">
@@ -1127,52 +1127,52 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7672089609104129</v>
+        <v>0.8102563390992875</v>
       </c>
       <c r="E11" t="n">
-        <v>0.004973036242139429</v>
+        <v>0.005350022911762434</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9254691575849276</v>
+        <v>0.9446026324439973</v>
       </c>
       <c r="G11" t="n">
-        <v>0.003646481622075709</v>
+        <v>0.002240480118703075</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8432462746004135</v>
+        <v>0.8581033800328084</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7040407092041608</v>
+        <v>0.7677332139963536</v>
       </c>
       <c r="J11" t="n">
-        <v>0.875074221587324</v>
+        <v>0.8948169219275567</v>
       </c>
       <c r="K11" t="n">
-        <v>32.026</v>
+        <v>42.487</v>
       </c>
       <c r="L11" t="n">
-        <v>5.32</v>
+        <v>6.92</v>
       </c>
       <c r="M11" t="n">
-        <v>0.774</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.9489</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8489</v>
+        <v>0.8514</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.7834</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8784999999999999</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6918</v>
+        <v>0.7443</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3064</v>
+        <v>0.2563</v>
       </c>
     </row>
     <row r="12">
@@ -1192,52 +1192,52 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7672089609104129</v>
+        <v>0.8102563390992875</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004973036242139429</v>
+        <v>0.005350022911762434</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9254691575849276</v>
+        <v>0.9446026324439973</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003646481622075709</v>
+        <v>0.002240480118703075</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8432462746004135</v>
+        <v>0.8581033800328084</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7040407092041608</v>
+        <v>0.7677332139963536</v>
       </c>
       <c r="J12" t="n">
-        <v>0.875074221587324</v>
+        <v>0.8948169219275567</v>
       </c>
       <c r="K12" t="n">
-        <v>39.122</v>
+        <v>26.029</v>
       </c>
       <c r="L12" t="n">
-        <v>5.01</v>
+        <v>6.65</v>
       </c>
       <c r="M12" t="n">
-        <v>0.774</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.9489</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8489</v>
+        <v>0.8514</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.7834</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8784999999999999</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6918</v>
+        <v>0.7443</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3064</v>
+        <v>0.2563</v>
       </c>
     </row>
     <row r="13">
@@ -1257,52 +1257,52 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.7693477151049755</v>
+        <v>0.813106416063533</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004717766394153992</v>
+        <v>0.003923118116496006</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9222753475760725</v>
+        <v>0.9433683738755994</v>
       </c>
       <c r="G13" t="n">
-        <v>0.004139844727486687</v>
+        <v>0.002063542596344094</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7834716267548076</v>
+        <v>0.8158289994304611</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7559101289146339</v>
+        <v>0.8105763475291026</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8674522288591666</v>
+        <v>0.8910245751238295</v>
       </c>
       <c r="K13" t="n">
-        <v>68.5</v>
+        <v>73.32599999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>5.01</v>
+        <v>6.79</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7702</v>
+        <v>0.8163</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9195</v>
+        <v>0.947</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7754</v>
+        <v>0.8048</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7651</v>
+        <v>0.8282</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.8665</v>
+        <v>0.891</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6761</v>
+        <v>0.7389</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3142</v>
+        <v>0.2687</v>
       </c>
     </row>
   </sheetData>
